--- a/Action_Output_PendingTimes.xlsx
+++ b/Action_Output_PendingTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BadrM8\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BF0FD1-EFE4-4613-83D8-248EDC8A4131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC50F87A-6BCD-4F81-9F0A-B50CE6B3A12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2640" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="313">
   <si>
     <t>TA-Ticketnr.</t>
   </si>
@@ -202,9 +202,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">TA0000017595444													</t>
-  </si>
-  <si>
     <t>TA0000017595444</t>
   </si>
   <si>
@@ -277,15 +274,9 @@
     <t>19:59:44</t>
   </si>
   <si>
-    <t xml:space="preserve">TA0000017621989												</t>
-  </si>
-  <si>
     <t>TA0000017621989</t>
   </si>
   <si>
-    <t xml:space="preserve">TA0000017641940												</t>
-  </si>
-  <si>
     <t>TA0000017641940</t>
   </si>
   <si>
@@ -400,9 +391,6 @@
     <t>02:05:02</t>
   </si>
   <si>
-    <t xml:space="preserve">TA0000017664078										</t>
-  </si>
-  <si>
     <t>TA0000017664078</t>
   </si>
   <si>
@@ -443,9 +431,6 @@
   </si>
   <si>
     <t>05:42:42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA0000017642768						</t>
   </si>
   <si>
     <t>TA0000017642768</t>
@@ -1001,21 +986,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1038,22 +1017,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1061,9 +1029,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1366,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -1427,109 +1392,117 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1540,86 +1513,130 @@
         <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>310</v>
       </c>
       <c r="K5">
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>311</v>
       </c>
       <c r="N5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2.680092592592592</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
-        <v>315</v>
+        <v>49</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>317</v>
+        <v>50</v>
       </c>
       <c r="M6" t="s">
-        <v>316</v>
+        <v>51</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2.680092592592592</v>
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -1628,633 +1645,763 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" t="s">
-        <v>59</v>
+        <v>70</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="M9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10">
+        <v>7</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12" t="s">
-        <v>71</v>
-      </c>
-      <c r="K12">
-        <v>7</v>
-      </c>
-      <c r="L12" t="s">
-        <v>72</v>
-      </c>
-      <c r="M12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12" t="s">
-        <v>74</v>
-      </c>
+      <c r="A12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K13">
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2.895833333333333</v>
+      </c>
+      <c r="G14" t="s">
+        <v>28</v>
       </c>
       <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" t="s">
+        <v>97</v>
+      </c>
+      <c r="N14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
         <v>35</v>
       </c>
-      <c r="I14" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" t="s">
-        <v>81</v>
-      </c>
-      <c r="K14">
+      <c r="I15" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16">
         <v>2</v>
       </c>
-      <c r="L14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="L16" t="s">
+        <v>106</v>
+      </c>
+      <c r="M16" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17">
+        <v>12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>115</v>
+      </c>
+      <c r="M17" t="s">
+        <v>116</v>
+      </c>
+      <c r="N17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s">
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="K18">
         <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="N18" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="2">
-        <v>2.895833333333333</v>
-      </c>
-      <c r="G19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" t="s">
-        <v>98</v>
-      </c>
-      <c r="K19">
-        <v>7</v>
-      </c>
-      <c r="L19" t="s">
-        <v>99</v>
-      </c>
-      <c r="M19" t="s">
-        <v>100</v>
-      </c>
-      <c r="N19" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="M20" t="s">
-        <v>105</v>
-      </c>
-      <c r="N20" t="s">
-        <v>106</v>
+        <v>127</v>
+      </c>
+      <c r="N20" s="4">
+        <v>13.894293981481482</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
         <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="J21" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L21" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" t="s">
-        <v>111</v>
+        <v>131</v>
+      </c>
+      <c r="N21" s="4">
+        <v>2.7416898148148148</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>114</v>
-      </c>
-      <c r="F22" t="s">
-        <v>115</v>
-      </c>
-      <c r="G22" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="J22" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="K22">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="M22" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="N22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L23" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="M23" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="N23" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4.0673958333333333</v>
+      </c>
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" t="s">
+        <v>151</v>
+      </c>
+      <c r="K24">
+        <v>11</v>
+      </c>
+      <c r="L24" t="s">
+        <v>152</v>
+      </c>
+      <c r="M24" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>155</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" t="s">
+        <v>160</v>
+      </c>
+      <c r="K25">
+        <v>9</v>
+      </c>
+      <c r="L25" t="s">
+        <v>145</v>
+      </c>
+      <c r="M25" t="s">
+        <v>161</v>
+      </c>
+      <c r="N25" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I26" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="J26" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L26" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="M26" t="s">
-        <v>131</v>
-      </c>
-      <c r="N26" s="4">
-        <v>13.894293981481482</v>
+        <v>169</v>
+      </c>
+      <c r="N26" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" t="s">
+        <v>173</v>
+      </c>
+      <c r="F27" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
       </c>
       <c r="H27" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="K27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L27" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="M27" t="s">
-        <v>135</v>
-      </c>
-      <c r="N27" s="4">
-        <v>2.7416898148148148</v>
+        <v>177</v>
+      </c>
+      <c r="N27" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I28" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="J28" t="s">
+        <v>184</v>
+      </c>
+      <c r="K28">
+        <v>9</v>
+      </c>
+      <c r="L28" t="s">
+        <v>176</v>
+      </c>
+      <c r="M28" t="s">
+        <v>185</v>
+      </c>
+      <c r="N28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>137</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>138</v>
-      </c>
-      <c r="M28" t="s">
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
         <v>139</v>
       </c>
-      <c r="N28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3.823263888888889</v>
+      </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>190</v>
+      </c>
+      <c r="J29" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29">
+        <v>9</v>
+      </c>
+      <c r="L29" t="s">
+        <v>145</v>
+      </c>
+      <c r="M29" t="s">
+        <v>191</v>
+      </c>
+      <c r="N29" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="E30" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="G30" t="s">
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="J30" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="K30">
         <v>9</v>
       </c>
       <c r="L30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="N30" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="2">
-        <v>4.0673958333333333</v>
+        <v>202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>203</v>
       </c>
       <c r="G31" t="s">
         <v>20</v>
@@ -2263,86 +2410,86 @@
         <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="J31" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="K31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L31" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="M31" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="N31" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="E32" t="s">
-        <v>162</v>
-      </c>
-      <c r="F32" t="s">
-        <v>163</v>
+        <v>209</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
         <v>29</v>
       </c>
       <c r="I32" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="J32" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="K32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L32" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="M32" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="N32" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="C33" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="G33" t="s">
         <v>20</v>
@@ -2351,174 +2498,156 @@
         <v>29</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="J33" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="K33">
         <v>10</v>
       </c>
       <c r="L33" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="N33" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" t="s">
-        <v>179</v>
+        <v>227</v>
+      </c>
+      <c r="F34" s="2">
+        <v>4.1056828703703703</v>
       </c>
       <c r="G34" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
         <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="J34" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="K34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L34" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
-      </c>
-      <c r="F35" t="s">
-        <v>187</v>
+        <v>233</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1.138935185185185</v>
       </c>
       <c r="G35" t="s">
         <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="J35" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="K35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L35" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="M35" t="s">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s">
-        <v>191</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>142</v>
-      </c>
-      <c r="B36" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" t="s">
-        <v>193</v>
-      </c>
-      <c r="E36" t="s">
-        <v>194</v>
-      </c>
-      <c r="F36" s="2">
-        <v>3.823263888888889</v>
-      </c>
-      <c r="G36" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="J36" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="K36">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>150</v>
+        <v>239</v>
       </c>
       <c r="M36" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="N36" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="F37" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
@@ -2527,710 +2656,373 @@
         <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="J37" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="K37">
         <v>9</v>
       </c>
       <c r="L37" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="M37" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="N37" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="F38" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H38" t="s">
         <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="J38" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="K38">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="M38" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="N38" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" t="s">
-        <v>212</v>
-      </c>
-      <c r="C39" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" t="s">
-        <v>214</v>
-      </c>
-      <c r="F39" s="2">
+        <v>215</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" t="s">
+        <v>254</v>
+      </c>
+      <c r="J39" t="s">
+        <v>255</v>
+      </c>
+      <c r="K39">
         <v>1</v>
       </c>
-      <c r="G39" t="s">
-        <v>28</v>
-      </c>
-      <c r="H39" t="s">
-        <v>29</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="L39" t="s">
+        <v>256</v>
+      </c>
+      <c r="M39" t="s">
+        <v>257</v>
+      </c>
+      <c r="N39" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>215</v>
       </c>
-      <c r="J39" t="s">
-        <v>216</v>
-      </c>
-      <c r="K39">
-        <v>10</v>
-      </c>
-      <c r="L39" t="s">
-        <v>217</v>
-      </c>
-      <c r="M39" t="s">
-        <v>218</v>
-      </c>
-      <c r="N39" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" t="s">
+        <v>259</v>
+      </c>
+      <c r="J40" t="s">
+        <v>260</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>256</v>
+      </c>
+      <c r="M40" t="s">
+        <v>261</v>
+      </c>
+      <c r="N40" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>220</v>
-      </c>
-      <c r="B41" t="s">
-        <v>221</v>
-      </c>
-      <c r="C41" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" t="s">
-        <v>222</v>
-      </c>
-      <c r="E41" t="s">
-        <v>223</v>
-      </c>
-      <c r="F41" t="s">
-        <v>224</v>
-      </c>
-      <c r="G41" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="J41" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="K41">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="M41" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="N41" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>220</v>
-      </c>
-      <c r="B42" t="s">
-        <v>230</v>
-      </c>
-      <c r="C42" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" t="s">
-        <v>231</v>
-      </c>
-      <c r="E42" t="s">
-        <v>232</v>
-      </c>
-      <c r="F42" s="2">
-        <v>4.1056828703703703</v>
-      </c>
-      <c r="G42" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="M42" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="N42" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>220</v>
-      </c>
-      <c r="B43" t="s">
-        <v>236</v>
-      </c>
-      <c r="C43" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" t="s">
-        <v>237</v>
-      </c>
-      <c r="E43" t="s">
-        <v>238</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.138935185185185</v>
-      </c>
-      <c r="G43" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="J43" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="K43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="M43" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="N43" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>275</v>
+      </c>
+      <c r="B44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" t="s">
+        <v>278</v>
+      </c>
+      <c r="F44" t="s">
+        <v>279</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I44" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="J44" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="K44">
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="M44" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="N44" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>220</v>
-      </c>
-      <c r="B45" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" t="s">
-        <v>154</v>
-      </c>
-      <c r="D45" t="s">
-        <v>248</v>
-      </c>
-      <c r="E45" t="s">
-        <v>249</v>
-      </c>
-      <c r="F45" t="s">
-        <v>250</v>
-      </c>
-      <c r="G45" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="J45" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="K45">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="M45" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="N45" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>220</v>
-      </c>
-      <c r="B46" t="s">
-        <v>253</v>
-      </c>
-      <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" t="s">
-        <v>254</v>
-      </c>
-      <c r="E46" t="s">
-        <v>255</v>
-      </c>
-      <c r="F46" t="s">
-        <v>256</v>
-      </c>
-      <c r="G46" t="s">
-        <v>28</v>
+        <v>275</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="J46" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L46" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="M46" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="N46" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="H47" t="s">
         <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="J47" t="s">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="K47">
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="N47" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="H48" t="s">
         <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="J48" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L48" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s">
-        <v>267</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="H49" t="s">
         <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="J49" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L49" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="M49" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="N49" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>220</v>
-      </c>
-      <c r="H50" t="s">
-        <v>35</v>
-      </c>
-      <c r="I50" t="s">
-        <v>272</v>
-      </c>
-      <c r="J50" t="s">
-        <v>273</v>
-      </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="L50" t="s">
-        <v>261</v>
-      </c>
-      <c r="M50" t="s">
-        <v>274</v>
-      </c>
-      <c r="N50" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>220</v>
-      </c>
-      <c r="H51" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" t="s">
-        <v>276</v>
-      </c>
-      <c r="J51" t="s">
-        <v>277</v>
-      </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51" t="s">
-        <v>261</v>
-      </c>
-      <c r="M51" t="s">
-        <v>278</v>
-      </c>
-      <c r="N51" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>280</v>
-      </c>
-      <c r="B53" t="s">
-        <v>281</v>
-      </c>
-      <c r="C53" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" t="s">
-        <v>282</v>
-      </c>
-      <c r="E53" t="s">
-        <v>283</v>
-      </c>
-      <c r="F53" t="s">
-        <v>284</v>
-      </c>
-      <c r="G53" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I53" t="s">
-        <v>285</v>
-      </c>
-      <c r="J53" t="s">
-        <v>286</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53" t="s">
-        <v>287</v>
-      </c>
-      <c r="M53" t="s">
-        <v>288</v>
-      </c>
-      <c r="N53" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>280</v>
-      </c>
-      <c r="H54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I54" t="s">
-        <v>290</v>
-      </c>
-      <c r="J54" t="s">
-        <v>291</v>
-      </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
-      <c r="L54" t="s">
-        <v>301</v>
-      </c>
-      <c r="M54" t="s">
-        <v>292</v>
-      </c>
-      <c r="N54" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>280</v>
-      </c>
-      <c r="H55" t="s">
-        <v>35</v>
-      </c>
-      <c r="I55" t="s">
         <v>294</v>
       </c>
-      <c r="J55" t="s">
-        <v>295</v>
-      </c>
-      <c r="K55">
-        <v>7</v>
-      </c>
-      <c r="L55" t="s">
-        <v>300</v>
-      </c>
-      <c r="M55" t="s">
-        <v>302</v>
-      </c>
-      <c r="N55" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>280</v>
-      </c>
-      <c r="H56" t="s">
-        <v>35</v>
-      </c>
-      <c r="I56" t="s">
-        <v>303</v>
-      </c>
-      <c r="J56" t="s">
-        <v>304</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56" t="s">
-        <v>305</v>
-      </c>
-      <c r="M56" t="s">
-        <v>306</v>
-      </c>
-      <c r="N56" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>280</v>
-      </c>
-      <c r="H57" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" t="s">
-        <v>308</v>
-      </c>
-      <c r="J57" t="s">
-        <v>309</v>
-      </c>
-      <c r="K57">
-        <v>7</v>
-      </c>
-      <c r="L57" t="s">
-        <v>310</v>
-      </c>
-      <c r="M57" t="s">
-        <v>311</v>
-      </c>
-      <c r="N57" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>280</v>
-      </c>
-      <c r="H58" t="s">
-        <v>35</v>
-      </c>
-      <c r="I58" t="s">
-        <v>297</v>
-      </c>
-      <c r="J58" t="s">
-        <v>298</v>
-      </c>
-      <c r="K58">
-        <v>7</v>
-      </c>
-      <c r="L58" t="s">
-        <v>313</v>
-      </c>
-      <c r="M58" t="s">
-        <v>314</v>
-      </c>
-      <c r="N58" t="s">
-        <v>299</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="A52:N52"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A17:N17"/>
-    <mergeCell ref="A24:N24"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
